--- a/data/azucena/output/azucena_gto.xlsx
+++ b/data/azucena/output/azucena_gto.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dfa238\pyproj\gambit_tekken8\data\azucena\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38992B06-3D11-47BB-9F1A-245C2DD65FA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8CAF0AD-EDCA-45B9-8AFF-897158356F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12900" yWindow="2700" windowWidth="15900" windowHeight="11925" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20775" yWindow="2280" windowWidth="19320" windowHeight="11925" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Azucena Heat Engager (+17)" sheetId="1" r:id="rId1"/>
@@ -1354,7 +1354,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
-    <col min="2" max="2" width="90" customWidth="1"/>
+    <col min="2" max="2" width="77.85546875" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
   </cols>
@@ -1780,7 +1780,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" customWidth="1"/>
-    <col min="2" max="2" width="107.85546875" customWidth="1"/>
+    <col min="2" max="2" width="67.5703125" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
   </cols>

--- a/data/azucena/output/azucena_gto.xlsx
+++ b/data/azucena/output/azucena_gto.xlsx
@@ -8,26 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dfa238\pyproj\gambit_tekken8\data\azucena\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED003557-6212-4CB3-A2DE-C1FE4300DDE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42F0999F-AD44-4D4A-A5BF-333414DD2612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28740" yWindow="1125" windowWidth="28365" windowHeight="14355" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2070" yWindow="555" windowWidth="25620" windowHeight="14355" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Azucena 1,2~B BT (+8) on Reina" sheetId="1" r:id="rId1"/>
     <sheet name="Azucena BT4 on block (-5) on Re" sheetId="2" r:id="rId2"/>
-    <sheet name="Azucena db3 (+4) into BT on Rei" sheetId="3" r:id="rId3"/>
-    <sheet name="db3 on xiaoyu" sheetId="4" r:id="rId4"/>
-    <sheet name="Azucena LIB (+5) with Reina" sheetId="5" r:id="rId5"/>
-    <sheet name="Azucena LIB (+8) with Reina" sheetId="6" r:id="rId6"/>
-    <sheet name="Azucena Oki BT on Wall (+6 BT)" sheetId="7" r:id="rId7"/>
-    <sheet name="Azu Oki BT on Wall no tech roll" sheetId="8" r:id="rId8"/>
+    <sheet name="d1 (+4) Crouch Mix" sheetId="3" r:id="rId3"/>
+    <sheet name="Azucena db3 (+4) into BT on Rei" sheetId="4" r:id="rId4"/>
+    <sheet name="db3 on xiaoyu" sheetId="5" r:id="rId5"/>
+    <sheet name="Azucena LIB (+5) with Reina" sheetId="6" r:id="rId6"/>
+    <sheet name="Azucena LIB (+8) with Reina" sheetId="7" r:id="rId7"/>
+    <sheet name="Azucena Oki BT on Wall (+6 BT)" sheetId="8" r:id="rId8"/>
+    <sheet name="Azu Oki BT on Wall no tech roll" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="74">
   <si>
     <t>Azucena 1,2~B BT (+8) on Reina</t>
   </si>
@@ -71,9 +72,15 @@
     <t>qcb</t>
   </si>
   <si>
+    <t>d1</t>
+  </si>
+  <si>
     <t>B</t>
   </si>
   <si>
+    <t>DB1</t>
+  </si>
+  <si>
     <t>Hop Kick</t>
   </si>
   <si>
@@ -104,6 +111,39 @@
     <t>b</t>
   </si>
   <si>
+    <t>d1 (+4) Crouch Mix</t>
+  </si>
+  <si>
+    <t>d1 (+4) on block Crouch Mix</t>
+  </si>
+  <si>
+    <t>fc df3</t>
+  </si>
+  <si>
+    <t>fc df4</t>
+  </si>
+  <si>
+    <t>ws1</t>
+  </si>
+  <si>
+    <t>ws2</t>
+  </si>
+  <si>
+    <t>ws3</t>
+  </si>
+  <si>
+    <t>uf3+4</t>
+  </si>
+  <si>
+    <t>DB</t>
+  </si>
+  <si>
+    <t>backdash</t>
+  </si>
+  <si>
+    <t>SSR~b</t>
+  </si>
+  <si>
     <t>Azucena db3 (+4) into BT on Reina</t>
   </si>
   <si>
@@ -117,15 +157,6 @@
   </si>
   <si>
     <t>BT.4</t>
-  </si>
-  <si>
-    <t>DB</t>
-  </si>
-  <si>
-    <t>DB1</t>
-  </si>
-  <si>
-    <t>SSR~b</t>
   </si>
   <si>
     <t>db3 on xiaoyu</t>
@@ -225,6 +256,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -347,7 +381,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -380,6 +414,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -682,7 +722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -720,7 +760,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="4">
-        <v>6.2</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="63" x14ac:dyDescent="0.25">
@@ -753,10 +793,10 @@
         <v>11</v>
       </c>
       <c r="C9" s="8">
-        <v>0.2695597746713958</v>
+        <v>0.22132072640330491</v>
       </c>
       <c r="D9" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -767,10 +807,10 @@
         <v>12</v>
       </c>
       <c r="C10" s="8">
-        <v>0.4681827665345295</v>
+        <v>0.25047572329486772</v>
       </c>
       <c r="D10" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -781,24 +821,24 @@
         <v>13</v>
       </c>
       <c r="C11" s="8">
-        <v>0.26225745879407469</v>
+        <v>0.18434608696310101</v>
       </c>
       <c r="D11" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="3" t="s">
+      <c r="A12" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="9">
-        <v>0.77446275818902566</v>
-      </c>
-      <c r="D12" s="3">
-        <v>-6</v>
+      <c r="C12" s="8">
+        <v>0.34385746333872641</v>
+      </c>
+      <c r="D12" s="2">
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -809,10 +849,10 @@
         <v>15</v>
       </c>
       <c r="C13" s="9">
-        <v>9.1174629668266227E-2</v>
+        <v>0.75448642691137358</v>
       </c>
       <c r="D13" s="3">
-        <v>-6</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -823,10 +863,38 @@
         <v>16</v>
       </c>
       <c r="C14" s="9">
-        <v>0.13436261214270809</v>
+        <v>5.9636596582862862E-2</v>
       </c>
       <c r="D14" s="3">
-        <v>-6</v>
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="9">
+        <v>0.1011534634799616</v>
+      </c>
+      <c r="D15" s="3">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="9">
+        <v>8.4723513025801916E-2</v>
+      </c>
+      <c r="D16" s="3">
+        <v>-7</v>
       </c>
     </row>
   </sheetData>
@@ -850,7 +918,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -885,7 +953,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -907,7 +975,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C9" s="8">
         <v>0.62542769479266946</v>
@@ -935,7 +1003,7 @@
         <v>2</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C11" s="8">
         <v>0.1205008671072509</v>
@@ -949,7 +1017,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C12" s="8">
         <v>0.13197696847767701</v>
@@ -963,7 +1031,7 @@
         <v>4</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C13" s="9">
         <v>0.29626945583161168</v>
@@ -977,7 +1045,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C14" s="9">
         <v>0.1172054990103079</v>
@@ -991,7 +1059,7 @@
         <v>4</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C15" s="9">
         <v>0.13542196215013749</v>
@@ -1005,7 +1073,7 @@
         <v>4</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C16" s="9">
         <v>0.45110308300794277</v>
@@ -1027,15 +1095,15 @@
   <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35" customWidth="1"/>
-    <col min="2" max="2" width="20.42578125" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -1062,15 +1130,15 @@
         <v>5</v>
       </c>
       <c r="B4" s="4">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="63" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1092,13 +1160,13 @@
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="8">
-        <v>2.275055707589126E-2</v>
+        <v>29</v>
+      </c>
+      <c r="C9" s="12">
+        <v>0.1845618796272232</v>
       </c>
       <c r="D9" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1106,13 +1174,13 @@
         <v>2</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="8">
-        <v>9.0374473612171699E-2</v>
+        <v>30</v>
+      </c>
+      <c r="C10" s="12">
+        <v>8.2734635694962116E-2</v>
       </c>
       <c r="D10" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1120,13 +1188,13 @@
         <v>2</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="8">
-        <v>0.24520044848460579</v>
+        <v>31</v>
+      </c>
+      <c r="C11" s="12">
+        <v>0.46558074953768142</v>
       </c>
       <c r="D11" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1134,13 +1202,13 @@
         <v>2</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="8">
-        <v>0.33752241484769008</v>
+        <v>32</v>
+      </c>
+      <c r="C12" s="12">
+        <v>5.4309743419132972E-2</v>
       </c>
       <c r="D12" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1148,13 +1216,13 @@
         <v>2</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="8">
-        <v>0.134355797244644</v>
+        <v>33</v>
+      </c>
+      <c r="C13" s="12">
+        <v>3.5780536840840538E-2</v>
       </c>
       <c r="D13" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1162,13 +1230,13 @@
         <v>2</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="8">
-        <v>0.1697963087349971</v>
+        <v>34</v>
+      </c>
+      <c r="C14" s="12">
+        <v>0.17703245488015981</v>
       </c>
       <c r="D14" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1176,13 +1244,13 @@
         <v>4</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="9">
-        <v>0.518669395161788</v>
+        <v>15</v>
+      </c>
+      <c r="C15" s="13">
+        <v>0.65027637576484965</v>
       </c>
       <c r="D15" s="3">
-        <v>-2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1190,13 +1258,13 @@
         <v>4</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" s="9">
-        <v>2.0393873812204082E-2</v>
+        <v>35</v>
+      </c>
+      <c r="C16" s="13">
+        <v>0.1131992578707188</v>
       </c>
       <c r="D16" s="3">
-        <v>-2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1204,13 +1272,13 @@
         <v>4</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="9">
-        <v>2.4100955634917771E-2</v>
+        <v>36</v>
+      </c>
+      <c r="C17" s="13">
+        <v>5.2055977696101242E-2</v>
       </c>
       <c r="D17" s="3">
-        <v>-2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1218,13 +1286,13 @@
         <v>4</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" s="9">
-        <v>8.0719745481810642E-2</v>
+        <v>37</v>
+      </c>
+      <c r="C18" s="13">
+        <v>9.0062451634080609E-2</v>
       </c>
       <c r="D18" s="3">
-        <v>-2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1232,13 +1300,13 @@
         <v>4</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" s="9">
-        <v>0.10270592876206271</v>
+        <v>17</v>
+      </c>
+      <c r="C19" s="13">
+        <v>2.0081917296374671E-3</v>
       </c>
       <c r="D19" s="3">
-        <v>-2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1246,13 +1314,13 @@
         <v>4</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="9">
-        <v>0.2534101011472169</v>
+        <v>18</v>
+      </c>
+      <c r="C20" s="13">
+        <v>9.2397745304612283E-2</v>
       </c>
       <c r="D20" s="3">
-        <v>-2</v>
+        <v>-5</v>
       </c>
     </row>
   </sheetData>
@@ -1265,6 +1333,247 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="35" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+    </row>
+    <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="173.25" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="8">
+        <v>2.275055707589126E-2</v>
+      </c>
+      <c r="D9" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="8">
+        <v>9.0374473612171699E-2</v>
+      </c>
+      <c r="D10" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="8">
+        <v>0.24520044848460579</v>
+      </c>
+      <c r="D11" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="8">
+        <v>0.33752241484769008</v>
+      </c>
+      <c r="D12" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="8">
+        <v>0.134355797244644</v>
+      </c>
+      <c r="D13" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="8">
+        <v>0.1697963087349971</v>
+      </c>
+      <c r="D14" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="9">
+        <v>0.518669395161788</v>
+      </c>
+      <c r="D15" s="3">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="9">
+        <v>2.0393873812204082E-2</v>
+      </c>
+      <c r="D16" s="3">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="9">
+        <v>2.4100955634917771E-2</v>
+      </c>
+      <c r="D17" s="3">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="9">
+        <v>8.0719745481810642E-2</v>
+      </c>
+      <c r="D18" s="3">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="9">
+        <v>0.10270592876206271</v>
+      </c>
+      <c r="D19" s="3">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="9">
+        <v>0.2534101011472169</v>
+      </c>
+      <c r="D20" s="3">
+        <v>-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1276,7 +1585,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -1295,7 +1604,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1311,7 +1620,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1333,7 +1642,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="C9" s="8">
         <v>1.6733382603152339E-2</v>
@@ -1347,7 +1656,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C10" s="8">
         <v>3.5021302027919893E-2</v>
@@ -1375,7 +1684,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C12" s="8">
         <v>0.3936374546665497</v>
@@ -1403,7 +1712,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C14" s="8">
         <v>4.0139722512292322E-2</v>
@@ -1428,10 +1737,10 @@
     </row>
     <row r="16" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" s="9">
         <v>0.50516445728569881</v>
@@ -1442,10 +1751,10 @@
     </row>
     <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="C17" s="9">
         <v>2.18003073288527E-2</v>
@@ -1456,10 +1765,10 @@
     </row>
     <row r="18" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C18" s="9">
         <v>0.1057412447211671</v>
@@ -1470,10 +1779,10 @@
     </row>
     <row r="19" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C19" s="9">
         <v>4.067691641392443E-2</v>
@@ -1484,10 +1793,10 @@
     </row>
     <row r="20" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C20" s="9">
         <v>0.26403740242830442</v>
@@ -1498,10 +1807,10 @@
     </row>
     <row r="21" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C21" s="9">
         <v>2.4579462928164451E-2</v>
@@ -1512,10 +1821,10 @@
     </row>
     <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C22" s="9">
         <v>3.8000208893888027E-2</v>
@@ -1532,8 +1841,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1545,7 +1854,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -1580,7 +1889,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1602,7 +1911,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C9" s="8">
         <v>0.52648277247297603</v>
@@ -1616,7 +1925,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="C10" s="8">
         <v>4.8123819109322952E-2</v>
@@ -1630,7 +1939,7 @@
         <v>2</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="C11" s="8">
         <v>0.1073844892529619</v>
@@ -1644,7 +1953,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C12" s="8">
         <v>2.2551914112684101E-2</v>
@@ -1658,7 +1967,7 @@
         <v>2</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C13" s="8">
         <v>0.14040118935484561</v>
@@ -1672,7 +1981,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C14" s="8">
         <v>0.15505581569720939</v>
@@ -1686,7 +1995,7 @@
         <v>4</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C15" s="9">
         <v>0.60294271540680533</v>
@@ -1700,7 +2009,7 @@
         <v>4</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C16" s="9">
         <v>0.17652739990321389</v>
@@ -1714,7 +2023,7 @@
         <v>4</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C17" s="9">
         <v>1.2903536282986549E-2</v>
@@ -1728,7 +2037,7 @@
         <v>4</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C18" s="9">
         <v>3.4003901320589898E-2</v>
@@ -1742,7 +2051,7 @@
         <v>4</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C19" s="9">
         <v>0.1065845567976542</v>
@@ -1756,169 +2065,12 @@
         <v>4</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C20" s="9">
         <v>6.7037890288750124E-2</v>
       </c>
       <c r="D20" s="3">
-        <v>-6</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="29" customWidth="1"/>
-    <col min="2" max="2" width="32.7109375" customWidth="1"/>
-    <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-    </row>
-    <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="4">
-        <v>5.7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="136.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="8">
-        <v>0.7681542528378168</v>
-      </c>
-      <c r="D9" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="8">
-        <v>0.1012284248172912</v>
-      </c>
-      <c r="D10" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="8">
-        <v>0.1306173223448919</v>
-      </c>
-      <c r="D11" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="9">
-        <v>0.72865806250971854</v>
-      </c>
-      <c r="D12" s="3">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="9">
-        <v>0.1744674234178199</v>
-      </c>
-      <c r="D13" s="3">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14" s="9">
-        <v>9.6874514072461518E-2</v>
-      </c>
-      <c r="D14" s="3">
         <v>-6</v>
       </c>
     </row>
@@ -1932,6 +2084,163 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="29" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+    </row>
+    <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="4">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="138" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="8">
+        <v>0.7681542528378168</v>
+      </c>
+      <c r="D9" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="8">
+        <v>0.1012284248172912</v>
+      </c>
+      <c r="D10" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="8">
+        <v>0.1306173223448919</v>
+      </c>
+      <c r="D11" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="9">
+        <v>0.72865806250971854</v>
+      </c>
+      <c r="D12" s="3">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="9">
+        <v>0.1744674234178199</v>
+      </c>
+      <c r="D13" s="3">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="9">
+        <v>9.6874514072461518E-2</v>
+      </c>
+      <c r="D14" s="3">
+        <v>-6</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1943,7 +2252,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -1978,7 +2287,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -2014,7 +2323,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C10" s="8">
         <v>9.510147814462816E-2</v>
@@ -2028,7 +2337,7 @@
         <v>2</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="C11" s="8">
         <v>4.4664119970088657E-2</v>
@@ -2042,7 +2351,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C12" s="8">
         <v>6.3868195568624997E-2</v>
@@ -2056,7 +2365,7 @@
         <v>2</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="C13" s="8">
         <v>0.33559785945850101</v>
@@ -2070,7 +2379,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C14" s="9">
         <v>1.608977329956289E-2</v>
@@ -2084,7 +2393,7 @@
         <v>4</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C15" s="9">
         <v>0.46913855979634311</v>
@@ -2098,7 +2407,7 @@
         <v>4</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C16" s="9">
         <v>0.1942776266134805</v>
@@ -2112,7 +2421,7 @@
         <v>4</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C17" s="9">
         <v>0.27444790893250748</v>
@@ -2126,7 +2435,7 @@
         <v>4</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C18" s="9">
         <v>4.6046131358106007E-2</v>
@@ -2143,8 +2452,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2156,7 +2465,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2191,7 +2500,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -2227,7 +2536,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C10" s="8">
         <v>0.71698113207547165</v>
@@ -2241,7 +2550,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C11" s="9">
         <v>0.96226415094339623</v>
@@ -2255,7 +2564,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C12" s="9">
         <v>3.7735849056603772E-2</v>
